--- a/public_reports/reports/history/build-local/Failed_Test_Cases.xlsx
+++ b/public_reports/reports/history/build-local/Failed_Test_Cases.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,286 +458,6 @@
         <is>
           <t>Execution Time (s)</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TC_AUTH_010</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Authentication</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Verify Authentication functionality - Scenario 10</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>P1 - High</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>AssertionError: OTP validation message expected 'Invalid OTP' but got 'Connection Timeout'</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>TC_AUTHZ_015</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Authorization</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Verify Authorization functionality - Scenario 15</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P2 - Medium</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>AssertionError: Access was granted with expired session token</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>3.05</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TC_FORM_008</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Forms</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Verify Forms functionality - Scenario 8</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P3 - Low</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>AssertionError: Required field border color should be #FF0000</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TC_VAL_018</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Input Validation</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Verify Input Validation functionality - Scenario 18</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1 - High</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ValidationError: Field failed SQL sanitization check</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>3.56</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>TC_UPLD_002</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>File Upload</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Verify File Upload functionality - Scenario 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P1 - High</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AppiumException: Application crash detected during 50MB file transfer</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TC_OFFL_005</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Offline Handling</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Verify Offline Handling functionality - Scenario 5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P0 - Critical</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>TimeoutException: Cache queue sync did not complete within 10 seconds</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>TC_PERF_012</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Performance Smoke Tests</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Verify Performance Smoke Tests functionality - Scenario 12</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P3 - Low</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>AssertionError: First meaningful paint took 680ms (Threshold: 500ms)</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>TC_REGRESS_035</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Regression Suite</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Verify Regression Suite functionality - Scenario 35</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>P2 - Medium</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>FAILED</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>HTTP 409 Conflict: Slot already locked by another thread</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2.95</v>
       </c>
     </row>
   </sheetData>
